--- a/data/trending_integrated_20260907_09.xlsx
+++ b/data/trending_integrated_20260907_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,60 +563,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25500</v>
+        <v>220500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+8.51%</t>
+          <t>+9.43%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E2" t="n">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>88</v>
       </c>
       <c r="G2" t="n">
-        <v>113</v>
+        <v>481</v>
       </c>
       <c r="H2" t="n">
-        <v>0.16</v>
+        <v>29.46</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>23500</v>
+        <v>201500</v>
       </c>
       <c r="K2" t="n">
-        <v>23200</v>
+        <v>212500</v>
       </c>
       <c r="L2" t="n">
-        <v>25500</v>
+        <v>222500</v>
       </c>
       <c r="M2" t="n">
-        <v>23000</v>
+        <v>212500</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>29.51</v>
       </c>
       <c r="O2" t="n">
-        <v>27429090425</v>
+        <v>78807675250</v>
       </c>
       <c r="P2" t="n">
-        <v>28750</v>
+        <v>438000</v>
       </c>
       <c r="Q2" t="n">
-        <v>8200</v>
+        <v>74700</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -626,20 +626,20 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스카이랩스, CART 혈압계 관련 뉴스 및 임상 연구 결과 발표. 신사업 진출 기대감 있으나, 적자 규모 대비 시가총액 논란 및 주가 변동성 우려 존재.</t>
+          <t>로봇 사업 진출 기대감에 따른 주가 상승 전망. 3분기 영업이익 호조 예상.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['CART', '임상연구', '신사업']</t>
+          <t>['로봇', '액츄에이터', '영업이익']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1738000</v>
+        <v>1748000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+5.53%</t>
+          <t>+6.13%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>636</v>
+        <v>723</v>
       </c>
       <c r="F3" t="n">
-        <v>403</v>
+        <v>448</v>
       </c>
       <c r="G3" t="n">
-        <v>2606</v>
+        <v>2796</v>
       </c>
       <c r="H3" t="n">
         <v>50.5</v>
@@ -693,16 +693,16 @@
         <v>1737000</v>
       </c>
       <c r="L3" t="n">
-        <v>1745000</v>
+        <v>1751000</v>
       </c>
       <c r="M3" t="n">
-        <v>1735000</v>
+        <v>1734000</v>
       </c>
       <c r="N3" t="n">
         <v>50.45</v>
       </c>
       <c r="O3" t="n">
-        <v>300358177500</v>
+        <v>751901631500</v>
       </c>
       <c r="P3" t="n">
         <v>2987000</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>266500</v>
+        <v>267250</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+4.31%</t>
+          <t>+4.60%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="F4" t="n">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="G4" t="n">
-        <v>2354</v>
+        <v>2426</v>
       </c>
       <c r="H4" t="n">
         <v>46.73</v>
@@ -788,13 +788,13 @@
         <v>267500</v>
       </c>
       <c r="M4" t="n">
-        <v>266500</v>
+        <v>265500</v>
       </c>
       <c r="N4" t="n">
         <v>46.71</v>
       </c>
       <c r="O4" t="n">
-        <v>140359478000</v>
+        <v>408600028750</v>
       </c>
       <c r="P4" t="n">
         <v>374500</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자, 3개월 보유 시 5% 배당 기대감 및 목표 주가 50~60만+a 전망. 단기적 주가 상승 기대감 존재하나, 검증 가능한 구체적 근거는 미흡.</t>
+          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['배당', '목표주가', '실적']</t>
+          <t>['배당', '목표주가', '상승']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,31 +839,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5170</v>
+        <v>23900</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-9.93%</t>
+          <t>+1.70%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="F5" t="n">
-        <v>25</v>
+        <v>79</v>
       </c>
       <c r="G5" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,28 +871,28 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5740</v>
+        <v>23500</v>
       </c>
       <c r="K5" t="n">
-        <v>5250</v>
+        <v>23200</v>
       </c>
       <c r="L5" t="n">
-        <v>5260</v>
+        <v>25600</v>
       </c>
       <c r="M5" t="n">
-        <v>5000</v>
+        <v>22800</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>503851040</v>
+        <v>97173794975</v>
       </c>
       <c r="P5" t="n">
-        <v>9680</v>
+        <v>28750</v>
       </c>
       <c r="Q5" t="n">
-        <v>371</v>
+        <v>8200</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -902,27 +902,119 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>본느, 반기보고서 제출 지연 악재 발생. 하한가 예상 및 주가 하락 우려 증폭. 긍정적인 매수세 유입 가능성은 낮음.</t>
+          <t>혈압계 뉴스 및 신사업 진출 관련 기대감. 시총 대비 적자 우려.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['혈압계', '신사업', '적자']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5290</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-7.84%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>54</v>
+      </c>
+      <c r="F6" t="n">
+        <v>29</v>
+      </c>
+      <c r="G6" t="n">
+        <v>109</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1252158300</v>
+      </c>
+      <c r="P6" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>371</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 악재 발생. 주가 하락세.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
         <v>0.1</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>['반기보고서', '악재', '하한가']</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
         <v>1</v>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated_20260907_09.xlsx
+++ b/data/trending_integrated_20260907_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z6"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>두산퓨얼셀</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>220500</v>
+        <v>50400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+9.43%</t>
+          <t>+14.94%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.05</v>
+        <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>140</v>
+        <v>51</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>481</v>
+        <v>172</v>
       </c>
       <c r="H2" t="n">
-        <v>29.46</v>
+        <v>14.18</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>201500</v>
+        <v>43850</v>
       </c>
       <c r="K2" t="n">
-        <v>212500</v>
+        <v>45650</v>
       </c>
       <c r="L2" t="n">
-        <v>222500</v>
+        <v>52300</v>
       </c>
       <c r="M2" t="n">
-        <v>212500</v>
+        <v>45650</v>
       </c>
       <c r="N2" t="n">
-        <v>29.51</v>
+        <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>78807675250</v>
+        <v>38270895575</v>
       </c>
       <c r="P2" t="n">
-        <v>438000</v>
+        <v>108900</v>
       </c>
       <c r="Q2" t="n">
-        <v>74700</v>
+        <v>18230</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>로봇 사업 진출 기대감에 따른 주가 상승 전망. 3분기 영업이익 호조 예상.</t>
+          <t>데이터센터 수주 기대감과 공매도 감소 추세. 5만원 돌파 및 연말 최고가 갱신 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['로봇', '액츄에이터', '영업이익']</t>
+          <t>['데이터센터', '수주', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>336260</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1748000</v>
+        <v>221000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+6.13%</t>
+          <t>+9.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E3" t="n">
-        <v>723</v>
+        <v>161</v>
       </c>
       <c r="F3" t="n">
-        <v>448</v>
+        <v>98</v>
       </c>
       <c r="G3" t="n">
-        <v>2796</v>
+        <v>515</v>
       </c>
       <c r="H3" t="n">
-        <v>50.5</v>
+        <v>29.46</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1647000</v>
+        <v>201500</v>
       </c>
       <c r="K3" t="n">
-        <v>1737000</v>
+        <v>212500</v>
       </c>
       <c r="L3" t="n">
-        <v>1751000</v>
+        <v>222500</v>
       </c>
       <c r="M3" t="n">
-        <v>1734000</v>
+        <v>212500</v>
       </c>
       <c r="N3" t="n">
-        <v>50.45</v>
+        <v>29.51</v>
       </c>
       <c r="O3" t="n">
-        <v>751901631500</v>
+        <v>110172002250</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>438000</v>
       </c>
       <c r="Q3" t="n">
-        <v>274000</v>
+        <v>74700</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>SK하이닉스, 외국인 매수세 유입 및 나스닥 선물 상승 출발 등 긍정적 신호 포착. 금주 200 돌파 전망 강하나, 구체적인 실적 기반 분석은 부족.</t>
+          <t>로봇 액츄에이터 사업 관련 긍정적 뉴스. 3분기 영업이익 컨센서스 상회 기대 및 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['외국인매수', '나스닥', '주가예측']</t>
+          <t>['로봇', '액츄에이터', '영업이익']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>267250</v>
+        <v>1744000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+4.60%</t>
+          <t>+5.89%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>552</v>
+        <v>798</v>
       </c>
       <c r="F4" t="n">
-        <v>345</v>
+        <v>484</v>
       </c>
       <c r="G4" t="n">
-        <v>2426</v>
+        <v>3024</v>
       </c>
       <c r="H4" t="n">
-        <v>46.73</v>
+        <v>50.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,51 +779,51 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>255500</v>
+        <v>1647000</v>
       </c>
       <c r="K4" t="n">
-        <v>267000</v>
+        <v>1737000</v>
       </c>
       <c r="L4" t="n">
-        <v>267500</v>
+        <v>1751000</v>
       </c>
       <c r="M4" t="n">
-        <v>265500</v>
+        <v>1734000</v>
       </c>
       <c r="N4" t="n">
-        <v>46.71</v>
+        <v>50.45</v>
       </c>
       <c r="O4" t="n">
-        <v>408600028750</v>
+        <v>970356252000</v>
       </c>
       <c r="P4" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>69600</v>
+        <v>274000</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>147000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
+          <t>외국인 매수세 유입 및 나스닥 선물 상승 출발. 연말 20만원 돌파 및 사상 최고가 갱신 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['배당', '목표주가', '상승']</t>
+          <t>['외국인', '나스닥', '자사주매입']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23900</v>
+        <v>266000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+1.70%</t>
+          <t>+4.11%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>121</v>
+        <v>599</v>
       </c>
       <c r="F5" t="n">
-        <v>79</v>
+        <v>369</v>
       </c>
       <c r="G5" t="n">
-        <v>135</v>
+        <v>2535</v>
       </c>
       <c r="H5" t="n">
-        <v>0.16</v>
+        <v>46.73</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>23500</v>
+        <v>255500</v>
       </c>
       <c r="K5" t="n">
-        <v>23200</v>
+        <v>267000</v>
       </c>
       <c r="L5" t="n">
-        <v>25600</v>
+        <v>268000</v>
       </c>
       <c r="M5" t="n">
-        <v>22800</v>
+        <v>265500</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="O5" t="n">
-        <v>97173794975</v>
+        <v>611300990250</v>
       </c>
       <c r="P5" t="n">
-        <v>28750</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>8200</v>
+        <v>69600</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>710000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>혈압계 뉴스 및 신사업 진출 관련 기대감. 시총 대비 적자 우려.</t>
+          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['혈압계', '신사업', '적자']</t>
+          <t>['배당', '목표주가', '상승']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5290</v>
+        <v>24100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-7.84%</t>
+          <t>+2.55%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>156</v>
       </c>
       <c r="F6" t="n">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="G6" t="n">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,58 +963,150 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>5740</v>
+        <v>23500</v>
       </c>
       <c r="K6" t="n">
-        <v>5250</v>
+        <v>23200</v>
       </c>
       <c r="L6" t="n">
-        <v>5420</v>
+        <v>25600</v>
       </c>
       <c r="M6" t="n">
-        <v>5000</v>
+        <v>22800</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1252158300</v>
+        <v>129936625950</v>
       </c>
       <c r="P6" t="n">
-        <v>9680</v>
+        <v>28750</v>
       </c>
       <c r="Q6" t="n">
-        <v>371</v>
+        <v>8200</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-13000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 악재 발생. 주가 하락세.</t>
+          <t>CART 혈압계 관련 뉴스 호재. 그러나 단기 하락 가능성 및 횡보장 우려도 존재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '주가 하락']</t>
+          <t>['CART', '혈압계', '뉴스']</t>
         </is>
       </c>
       <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5220</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-9.06%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>56</v>
+      </c>
+      <c r="F7" t="n">
+        <v>29</v>
+      </c>
+      <c r="G7" t="n">
+        <v>129</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L7" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1512181950</v>
+      </c>
+      <c r="P7" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>371</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 악재 발생. 조선일보 기사 통해 하한가 및 상장폐지 가능성 제기.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재', '조선일보']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated_20260907_09.xlsx
+++ b/data/trending_integrated_20260907_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>50400</v>
+        <v>52000</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+14.94%</t>
+          <t>+18.59%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>172</v>
+        <v>224</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>38270895575</v>
+        <v>47109199625</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>데이터센터 수주 기대감과 공매도 감소 추세. 5만원 돌파 및 연말 최고가 갱신 전망.</t>
+          <t>매수세 유입 및 5% 돌파 후 수익 전환 기대. 전고점 돌파 및 연말 사상 최고가 갱신 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['데이터센터', '수주', '공매도']</t>
+          <t>['공매도', '추세', '최고가']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,83 +655,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>JW신약</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>221000</v>
+        <v>3770</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+9.68%</t>
+          <t>+15.47%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.05</v>
+        <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>161</v>
+        <v>43</v>
       </c>
       <c r="F3" t="n">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="G3" t="n">
-        <v>515</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
-        <v>29.46</v>
+        <v>1.25</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>201500</v>
+        <v>3265</v>
       </c>
       <c r="K3" t="n">
-        <v>212500</v>
+        <v>3200</v>
       </c>
       <c r="L3" t="n">
-        <v>222500</v>
+        <v>3900</v>
       </c>
       <c r="M3" t="n">
-        <v>212500</v>
+        <v>3185</v>
       </c>
       <c r="N3" t="n">
-        <v>29.51</v>
+        <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>110172002250</v>
+        <v>94555482044</v>
       </c>
       <c r="P3" t="n">
-        <v>438000</v>
+        <v>3900</v>
       </c>
       <c r="Q3" t="n">
-        <v>74700</v>
+        <v>1246</v>
       </c>
       <c r="R3" t="n">
-        <v>190000</v>
+        <v>419000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>로봇 액츄에이터 사업 관련 긍정적 뉴스. 3분기 영업이익 컨센서스 상회 기대 및 주가 상승 전망.</t>
+          <t>탈모약 관련 기대감 및 3연상 가능성 언급. 5천원 목표가 설정 및 10% 이상 상승.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['로봇', '액츄에이터', '영업이익']</t>
+          <t>['탈모약', '3연상', '목표가']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>066570</t>
+          <t>067290</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1744000</v>
+        <v>224500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+5.89%</t>
+          <t>+11.41%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>798</v>
+        <v>204</v>
       </c>
       <c r="F4" t="n">
-        <v>484</v>
+        <v>126</v>
       </c>
       <c r="G4" t="n">
-        <v>3024</v>
+        <v>576</v>
       </c>
       <c r="H4" t="n">
-        <v>50.5</v>
+        <v>29.46</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,38 +779,38 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1647000</v>
+        <v>201500</v>
       </c>
       <c r="K4" t="n">
-        <v>1737000</v>
+        <v>212500</v>
       </c>
       <c r="L4" t="n">
-        <v>1751000</v>
+        <v>225500</v>
       </c>
       <c r="M4" t="n">
-        <v>1734000</v>
+        <v>212500</v>
       </c>
       <c r="N4" t="n">
-        <v>50.45</v>
+        <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>970356252000</v>
+        <v>162543542750</v>
       </c>
       <c r="P4" t="n">
-        <v>2987000</v>
+        <v>438000</v>
       </c>
       <c r="Q4" t="n">
-        <v>274000</v>
+        <v>74700</v>
       </c>
       <c r="R4" t="n">
-        <v>147000</v>
+        <v>190000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 나스닥 선물 상승 출발. 연말 20만원 돌파 및 사상 최고가 갱신 기대.</t>
+          <t>로봇 액츄에이터 부품 사업 관련 뉴스 기반 23만 탈환 기대. 3분기 영업이익 컨센서스 1조 1천억 예상.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['외국인', '나스닥', '자사주매입']</t>
+          <t>['로봇', '액츄에이터', '컨센서스']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066570</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>266000</v>
+        <v>1743000</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+4.11%</t>
+          <t>+5.83%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E5" t="n">
-        <v>599</v>
+        <v>796</v>
       </c>
       <c r="F5" t="n">
-        <v>369</v>
+        <v>469</v>
       </c>
       <c r="G5" t="n">
-        <v>2535</v>
+        <v>2634</v>
       </c>
       <c r="H5" t="n">
-        <v>46.73</v>
+        <v>50.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>255500</v>
+        <v>1647000</v>
       </c>
       <c r="K5" t="n">
-        <v>267000</v>
+        <v>1737000</v>
       </c>
       <c r="L5" t="n">
-        <v>268000</v>
+        <v>1751000</v>
       </c>
       <c r="M5" t="n">
-        <v>265500</v>
+        <v>1734000</v>
       </c>
       <c r="N5" t="n">
-        <v>46.71</v>
+        <v>50.45</v>
       </c>
       <c r="O5" t="n">
-        <v>611300990250</v>
+        <v>1152379595000</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q5" t="n">
-        <v>69600</v>
+        <v>274000</v>
       </c>
       <c r="R5" t="n">
-        <v>710000</v>
+        <v>147000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
+          <t>외국인 매수세 유입 및 ADR 상승에 따른 주가 상승 기대. 200 돌파 및 180만원 목표 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['배당', '목표주가', '상승']</t>
+          <t>['외국인', 'ADR', '주가예측']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24100</v>
+        <v>266000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+2.55%</t>
+          <t>+4.11%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E6" t="n">
-        <v>156</v>
+        <v>643</v>
       </c>
       <c r="F6" t="n">
-        <v>89</v>
+        <v>394</v>
       </c>
       <c r="G6" t="n">
-        <v>172</v>
+        <v>2687</v>
       </c>
       <c r="H6" t="n">
-        <v>0.16</v>
+        <v>46.73</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>23500</v>
+        <v>255500</v>
       </c>
       <c r="K6" t="n">
-        <v>23200</v>
+        <v>267000</v>
       </c>
       <c r="L6" t="n">
-        <v>25600</v>
+        <v>268000</v>
       </c>
       <c r="M6" t="n">
-        <v>22800</v>
+        <v>265500</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="O6" t="n">
-        <v>129936625950</v>
+        <v>774384559500</v>
       </c>
       <c r="P6" t="n">
-        <v>28750</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>8200</v>
+        <v>69600</v>
       </c>
       <c r="R6" t="n">
-        <v>-13000</v>
+        <v>710000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 호재. 그러나 단기 하락 가능성 및 횡보장 우려도 존재.</t>
+          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['CART', '혈압계', '뉴스']</t>
+          <t>['배당', '목표주가', '상승']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5220</v>
+        <v>23700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-9.06%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>173</v>
       </c>
       <c r="F7" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="G7" t="n">
-        <v>129</v>
+        <v>197</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,28 +1055,28 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5740</v>
+        <v>23500</v>
       </c>
       <c r="K7" t="n">
-        <v>5250</v>
+        <v>23200</v>
       </c>
       <c r="L7" t="n">
-        <v>5420</v>
+        <v>25600</v>
       </c>
       <c r="M7" t="n">
-        <v>5000</v>
+        <v>22800</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1512181950</v>
+        <v>148262170750</v>
       </c>
       <c r="P7" t="n">
-        <v>9680</v>
+        <v>28750</v>
       </c>
       <c r="Q7" t="n">
-        <v>371</v>
+        <v>8200</v>
       </c>
       <c r="R7" t="n">
         <v>-13000</v>
@@ -1086,27 +1086,119 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 악재 발생. 조선일보 기사 통해 하한가 및 상장폐지 가능성 제기.</t>
+          <t>CART 혈압계 관련 뉴스 언급. 일부 투자자는 하락 및 고평가 주장.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '조선일보']</t>
+          <t>['CART', '혈압계', '의료기기']</t>
         </is>
       </c>
       <c r="X7" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5280</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-8.01%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>58</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>141</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L8" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1772900000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>371</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 및 악재 뉴스 출현으로 인한 하한가 가능성 제기. 일부 투자자는 탈출.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재', '하한가']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>1</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated_20260907_09.xlsx
+++ b/data/trending_integrated_20260907_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z8"/>
+  <dimension ref="A1:Z14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52000</v>
+        <v>54300</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+18.59%</t>
+          <t>+23.83%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="F2" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G2" t="n">
-        <v>224</v>
+        <v>258</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -601,7 +601,7 @@
         <v>45650</v>
       </c>
       <c r="L2" t="n">
-        <v>52300</v>
+        <v>54400</v>
       </c>
       <c r="M2" t="n">
         <v>45650</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>47109199625</v>
+        <v>62590887375</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>매수세 유입 및 5% 돌파 후 수익 전환 기대. 전고점 돌파 및 연말 사상 최고가 갱신 전망.</t>
+          <t>두산퓨얼셀, 전고점 10만원 돌파 및 사상최고가 갱신 전망. 공매도 언급과 함께 5% 수익 실현 및 46000원 매수 완료 기록.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['공매도', '추세', '최고가']</t>
+          <t>['전고점', '사상최고가', '공매도']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3770</v>
+        <v>3715</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+15.47%</t>
+          <t>+13.78%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>94555482044</v>
+        <v>111050001406</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>탈모약 관련 기대감 및 3연상 가능성 언급. 5천원 목표가 설정 및 10% 이상 상승.</t>
+          <t>JW신약, 탈모약 대장으로서 3연상 및 5천원 목표 전망. 월가 상승 및 삼익과의 비교 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['탈모약', '3연상', '목표가']</t>
+          <t>['탈모약', '3연상', '5천원']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>224500</v>
+        <v>223000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+11.41%</t>
+          <t>+10.67%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="F4" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="G4" t="n">
-        <v>576</v>
+        <v>636</v>
       </c>
       <c r="H4" t="n">
         <v>29.46</v>
@@ -794,7 +794,7 @@
         <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>162543542750</v>
+        <v>193173066500</v>
       </c>
       <c r="P4" t="n">
         <v>438000</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>로봇 액츄에이터 부품 사업 관련 뉴스 기반 23만 탈환 기대. 3분기 영업이익 컨센서스 1조 1천억 예상.</t>
+          <t>LG전자, 로봇 액츄에이터 부품 기술력 기반 23만원 탈환 및 40만원 목표 전망. CES 2023 관련 뉴스 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇', '액츄에이터', '컨센서스']</t>
+          <t>['로봇 액츄에이터', 'CES 2023', '23만원']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,70 +839,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1743000</v>
+        <v>6350</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>+5.83%</t>
+          <t>+8.55%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="E5" t="n">
-        <v>796</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>469</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>2634</v>
+        <v>149</v>
       </c>
       <c r="H5" t="n">
-        <v>50.5</v>
+        <v>1.61</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1647000</v>
+        <v>5850</v>
       </c>
       <c r="K5" t="n">
-        <v>1737000</v>
+        <v>6000</v>
       </c>
       <c r="L5" t="n">
-        <v>1751000</v>
+        <v>6480</v>
       </c>
       <c r="M5" t="n">
-        <v>1734000</v>
+        <v>5940</v>
       </c>
       <c r="N5" t="n">
-        <v>50.45</v>
+        <v>2.31</v>
       </c>
       <c r="O5" t="n">
-        <v>1152379595000</v>
+        <v>7841899440</v>
       </c>
       <c r="P5" t="n">
-        <v>2987000</v>
+        <v>21500</v>
       </c>
       <c r="Q5" t="n">
-        <v>274000</v>
+        <v>2300</v>
       </c>
       <c r="R5" t="n">
-        <v>147000</v>
+        <v>-24000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외국인 매수세 유입 및 ADR 상승에 따른 주가 상승 기대. 200 돌파 및 180만원 목표 전망.</t>
+          <t>신약 개발 관련 기대감과 함께 '주당 1억' 등 높은 목표 가격 제시. 공매도 언급 및 저점 매수 권유.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외국인', 'ADR', '주가예측']</t>
+          <t>['신약 개발', '임상2상', '공매견']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>266000</v>
+        <v>1738000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+4.11%</t>
+          <t>+5.53%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>643</v>
+        <v>796</v>
       </c>
       <c r="F6" t="n">
-        <v>394</v>
+        <v>459</v>
       </c>
       <c r="G6" t="n">
-        <v>2687</v>
+        <v>2172</v>
       </c>
       <c r="H6" t="n">
-        <v>46.73</v>
+        <v>50.5</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>255500</v>
+        <v>1647000</v>
       </c>
       <c r="K6" t="n">
-        <v>267000</v>
+        <v>1737000</v>
       </c>
       <c r="L6" t="n">
-        <v>268000</v>
+        <v>1751000</v>
       </c>
       <c r="M6" t="n">
-        <v>265500</v>
+        <v>1734000</v>
       </c>
       <c r="N6" t="n">
-        <v>46.71</v>
+        <v>50.45</v>
       </c>
       <c r="O6" t="n">
-        <v>774384559500</v>
+        <v>1295662124500</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q6" t="n">
-        <v>69600</v>
+        <v>274000</v>
       </c>
       <c r="R6" t="n">
-        <v>710000</v>
+        <v>147000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>단기적 상승 및 목표주가 상향 전망. 5% 배당 기대.</t>
+          <t>SK하이닉스, 자사주 매입 및 200만원 돌파 예상. 외인 매집과 함께 170만원대 매수 및 매도 관련 논의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['배당', '목표주가', '상승']</t>
+          <t>['자사주 매입', '200만원', '외인 매집']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23700</v>
+        <v>83200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+0.85%</t>
+          <t>+5.05%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="F7" t="n">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="G7" t="n">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="H7" t="n">
-        <v>0.16</v>
+        <v>23.53</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>23500</v>
+        <v>79200</v>
       </c>
       <c r="K7" t="n">
-        <v>23200</v>
+        <v>80200</v>
       </c>
       <c r="L7" t="n">
-        <v>25600</v>
+        <v>84300</v>
       </c>
       <c r="M7" t="n">
-        <v>22800</v>
+        <v>79000</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>23.61</v>
       </c>
       <c r="O7" t="n">
-        <v>148262170750</v>
+        <v>79127864800</v>
       </c>
       <c r="P7" t="n">
-        <v>28750</v>
+        <v>139200</v>
       </c>
       <c r="Q7" t="n">
-        <v>8200</v>
+        <v>57000</v>
       </c>
       <c r="R7" t="n">
-        <v>-13000</v>
+        <v>21000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>CART 혈압계 관련 뉴스 언급. 일부 투자자는 하락 및 고평가 주장.</t>
+          <t>두산에너빌리티, 하반기 본 수주 및 10만원 돌파 전망. 두산퓨얼셀과의 비교 및 원전 건설 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['CART', '혈압계', '의료기기']</t>
+          <t>['하반기 수주', '원전 건설', '10만원']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5280</v>
+        <v>23400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-8.01%</t>
+          <t>+4.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G8" t="n">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5740</v>
+        <v>22500</v>
       </c>
       <c r="K8" t="n">
-        <v>5250</v>
+        <v>23100</v>
       </c>
       <c r="L8" t="n">
-        <v>5420</v>
+        <v>24000</v>
       </c>
       <c r="M8" t="n">
-        <v>5000</v>
+        <v>21500</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O8" t="n">
-        <v>1772900000</v>
+        <v>87574922750</v>
       </c>
       <c r="P8" t="n">
-        <v>9680</v>
+        <v>50600</v>
       </c>
       <c r="Q8" t="n">
-        <v>371</v>
+        <v>9070</v>
       </c>
       <c r="R8" t="n">
-        <v>-13000</v>
+        <v>-22000</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 및 악재 뉴스 출현으로 인한 하한가 가능성 제기. 일부 투자자는 탈출.</t>
+          <t>원익홀딩스, 로봇주 폭발 및 신사업 진출 재료 기반 상승 전망. 국민성장펀드 3500억 유일무이 상장사 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,18 +1187,570 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '하한가']</t>
+          <t>['로봇주', '신사업', '국민성장펀드']</t>
         </is>
       </c>
       <c r="X8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>030530</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>265250</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>+3.82%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E9" t="n">
+        <v>678</v>
+      </c>
+      <c r="F9" t="n">
+        <v>410</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2783</v>
+      </c>
+      <c r="H9" t="n">
+        <v>46.73</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>255500</v>
+      </c>
+      <c r="K9" t="n">
+        <v>267000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>268000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>264500</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46.71</v>
+      </c>
+      <c r="O9" t="n">
+        <v>891462676250</v>
+      </c>
+      <c r="P9" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>69600</v>
+      </c>
+      <c r="R9" t="n">
+        <v>710000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>삼성전자, 30만원 터치 및 50~60만+a 목표주가 언급. 배당 기대와 함께 단기 매도 의견도 혼재.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['목표주가', '배당', '매도']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>스카이랩스</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>23850</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+1.49%</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>184</v>
+      </c>
+      <c r="F10" t="n">
+        <v>98</v>
+      </c>
+      <c r="G10" t="n">
+        <v>228</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>23500</v>
+      </c>
+      <c r="K10" t="n">
+        <v>23200</v>
+      </c>
+      <c r="L10" t="n">
+        <v>25600</v>
+      </c>
+      <c r="M10" t="n">
+        <v>22800</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>162298431025</v>
+      </c>
+      <c r="P10" t="n">
+        <v>28750</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8200</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>스카이랩스, CART 혈압계 뉴스 언급에도 불구하고 적자 기업 고평가 및 하락 전망. 주포 변태 언급.</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>['CART 혈압계', '적자 기업', '하락']</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>386380</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>금호건설</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>16190</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>+0.62%</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F11" t="n">
+        <v>31</v>
+      </c>
+      <c r="G11" t="n">
+        <v>200</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>16090</v>
+      </c>
+      <c r="K11" t="n">
+        <v>16150</v>
+      </c>
+      <c r="L11" t="n">
+        <v>16480</v>
+      </c>
+      <c r="M11" t="n">
+        <v>15830</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>18330240905</v>
+      </c>
+      <c r="P11" t="n">
+        <v>19380</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3200</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>금호건설, 9월 메가특구법 발의 및 호남 반도체 산단 인프라 언급. 일부에서는 재탕글과 하방 예상.</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['메가특구법', '반도체 산단', '하방']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>002990</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>바이오니아</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>10380</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>-0.10%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F12" t="n">
+        <v>31</v>
+      </c>
+      <c r="G12" t="n">
+        <v>88</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>10390</v>
+      </c>
+      <c r="K12" t="n">
+        <v>10050</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9770</v>
+      </c>
+      <c r="N12" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>14608303835</v>
+      </c>
+      <c r="P12" t="n">
+        <v>15640</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5470</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-16000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>주가 상승 및 거래량 증가에 대한 기대감 표출. 다만, 공매도 관련 부정적 언급도 존재.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['주포', '공매도', '순환매']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
         <v>1</v>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>064550</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>아난티</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5410</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>-5.25%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E13" t="n">
+        <v>42</v>
+      </c>
+      <c r="F13" t="n">
+        <v>34</v>
+      </c>
+      <c r="G13" t="n">
+        <v>126</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>5710</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5640</v>
+      </c>
+      <c r="L13" t="n">
+        <v>5650</v>
+      </c>
+      <c r="M13" t="n">
+        <v>5270</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O13" t="n">
+        <v>10064838020</v>
+      </c>
+      <c r="P13" t="n">
+        <v>10480</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3150</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-265000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>아난티, 북한 여행자 보험 및 금강산 관광 관련 언급. 외인, 연기금 매수세에도 불구하고 하락 및 주가 조작 의혹 제기.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['북한', '금강산', '주가 조작']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>025980</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5290</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-7.84%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>65</v>
+      </c>
+      <c r="F14" t="n">
+        <v>34</v>
+      </c>
+      <c r="G14" t="n">
+        <v>144</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L14" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1968597240</v>
+      </c>
+      <c r="P14" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>371</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 악재로 인한 하한가 및 급락. 조선일보 기사 인용 및 투자자들의 탈출 언급.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재', '조선일보']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
         <is>
           <t>226340</t>
         </is>

--- a/data/trending_integrated_20260907_09.xlsx
+++ b/data/trending_integrated_20260907_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z14"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54300</v>
+        <v>54600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>+23.83%</t>
+          <t>+24.52%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.47</v>
       </c>
       <c r="E2" t="n">
-        <v>85</v>
+        <v>109</v>
       </c>
       <c r="F2" t="n">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>258</v>
+        <v>349</v>
       </c>
       <c r="H2" t="n">
         <v>14.18</v>
@@ -601,7 +601,7 @@
         <v>45650</v>
       </c>
       <c r="L2" t="n">
-        <v>54400</v>
+        <v>55000</v>
       </c>
       <c r="M2" t="n">
         <v>45650</v>
@@ -610,7 +610,7 @@
         <v>13.71</v>
       </c>
       <c r="O2" t="n">
-        <v>62590887375</v>
+        <v>77772460625</v>
       </c>
       <c r="P2" t="n">
         <v>108900</v>
@@ -619,14 +619,14 @@
         <v>18230</v>
       </c>
       <c r="R2" t="n">
-        <v>67000</v>
+        <v>160000</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>31000</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>두산퓨얼셀, 전고점 10만원 돌파 및 사상최고가 갱신 전망. 공매도 언급과 함께 5% 수익 실현 및 46000원 매수 완료 기록.</t>
+          <t>강한 상승 추세 속 공매도 세력과의 경쟁, 전고점 돌파 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['전고점', '사상최고가', '공매도']</t>
+          <t>['추세', '공매도', '전고점']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3715</v>
+        <v>3690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>+13.78%</t>
+          <t>+13.02%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.52</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H3" t="n">
         <v>1.25</v>
@@ -702,7 +702,7 @@
         <v>1.77</v>
       </c>
       <c r="O3" t="n">
-        <v>111050001406</v>
+        <v>121250479961</v>
       </c>
       <c r="P3" t="n">
         <v>3900</v>
@@ -711,23 +711,23 @@
         <v>1246</v>
       </c>
       <c r="R3" t="n">
-        <v>419000</v>
+        <v>179000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>JW신약, 탈모약 대장으로서 3연상 및 5천원 목표 전망. 월가 상승 및 삼익과의 비교 언급.</t>
+          <t>탈모약 관련 기대감 속에 주가 상승 모멘텀 형성, 거래량 부진 우려.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['탈모약', '3연상', '5천원']</t>
+          <t>['탈모약', '상승 모멘텀', '거래량']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>223000</v>
+        <v>221500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>+10.67%</t>
+          <t>+9.93%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="F4" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G4" t="n">
-        <v>636</v>
+        <v>686</v>
       </c>
       <c r="H4" t="n">
         <v>29.46</v>
@@ -794,7 +794,7 @@
         <v>29.51</v>
       </c>
       <c r="O4" t="n">
-        <v>193173066500</v>
+        <v>207350807500</v>
       </c>
       <c r="P4" t="n">
         <v>438000</v>
@@ -803,14 +803,14 @@
         <v>74700</v>
       </c>
       <c r="R4" t="n">
-        <v>190000</v>
+        <v>317000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>102000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>LG전자, 로봇 액츄에이터 부품 기술력 기반 23만원 탈환 및 40만원 목표 전망. CES 2023 관련 뉴스 언급.</t>
+          <t>로봇 액츄에이터 사업 관련 호재와 CES 2026 참가 소식으로 인한 급등세.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇 액츄에이터', 'CES 2023', '23만원']</t>
+          <t>['로봇', '액츄에이터', 'CES 2026']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,11 +839,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>페니트리움바이오</t>
+          <t>현대약품</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6350</v>
+        <v>8630</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -851,71 +851,71 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.7</v>
+        <v>-0.72</v>
       </c>
       <c r="E5" t="n">
         <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
-        <v>149</v>
+        <v>43</v>
       </c>
       <c r="H5" t="n">
-        <v>1.61</v>
+        <v>0.6</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>5850</v>
+        <v>7950</v>
       </c>
       <c r="K5" t="n">
-        <v>6000</v>
+        <v>8200</v>
       </c>
       <c r="L5" t="n">
-        <v>6480</v>
+        <v>9210</v>
       </c>
       <c r="M5" t="n">
-        <v>5940</v>
+        <v>7980</v>
       </c>
       <c r="N5" t="n">
-        <v>2.31</v>
+        <v>1.32</v>
       </c>
       <c r="O5" t="n">
-        <v>7841899440</v>
+        <v>66907313720</v>
       </c>
       <c r="P5" t="n">
-        <v>21500</v>
+        <v>15960</v>
       </c>
       <c r="Q5" t="n">
-        <v>2300</v>
+        <v>3500</v>
       </c>
       <c r="R5" t="n">
-        <v>-24000</v>
+        <v>208000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>신약 개발 관련 기대감과 함께 '주당 1억' 등 높은 목표 가격 제시. 공매도 언급 및 저점 매수 권유.</t>
+          <t>미프진 관련 소식 공식화 가능성에 대한 기대감 있으나, 주가 변동은 제한적.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['신약 개발', '임상2상', '공매견']</t>
+          <t>['미프진', '공식화']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,90 +924,90 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>187660</t>
+          <t>004310</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>페니트리움바이오</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1738000</v>
+        <v>6210</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+5.53%</t>
+          <t>+6.15%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="E6" t="n">
-        <v>796</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>459</v>
+        <v>32</v>
       </c>
       <c r="G6" t="n">
-        <v>2172</v>
+        <v>178</v>
       </c>
       <c r="H6" t="n">
-        <v>50.5</v>
+        <v>1.61</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1647000</v>
+        <v>5850</v>
       </c>
       <c r="K6" t="n">
-        <v>1737000</v>
+        <v>6000</v>
       </c>
       <c r="L6" t="n">
-        <v>1751000</v>
+        <v>6490</v>
       </c>
       <c r="M6" t="n">
-        <v>1734000</v>
+        <v>5940</v>
       </c>
       <c r="N6" t="n">
-        <v>50.45</v>
+        <v>2.31</v>
       </c>
       <c r="O6" t="n">
-        <v>1295662124500</v>
+        <v>9150073130</v>
       </c>
       <c r="P6" t="n">
-        <v>2987000</v>
+        <v>21500</v>
       </c>
       <c r="Q6" t="n">
-        <v>274000</v>
+        <v>2300</v>
       </c>
       <c r="R6" t="n">
-        <v>147000</v>
+        <v>-35000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>SK하이닉스, 자사주 매입 및 200만원 돌파 예상. 외인 매집과 함께 170만원대 매수 및 매도 관련 논의.</t>
+          <t>신약 개발 기대감이 있으나, 주가 상승에 대한 확신은 낮으며 보수적인 전망이 주를 이룹니다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['자사주 매입', '200만원', '외인 매집']</t>
+          <t>['신약 개발', '공매', '홀딩']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>187660</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83200</v>
+        <v>1736000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>+5.40%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.08</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>798</v>
       </c>
       <c r="F7" t="n">
-        <v>56</v>
+        <v>454</v>
       </c>
       <c r="G7" t="n">
-        <v>179</v>
+        <v>2107</v>
       </c>
       <c r="H7" t="n">
-        <v>23.53</v>
+        <v>50.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>79200</v>
+        <v>1647000</v>
       </c>
       <c r="K7" t="n">
-        <v>80200</v>
+        <v>1737000</v>
       </c>
       <c r="L7" t="n">
-        <v>84300</v>
+        <v>1751000</v>
       </c>
       <c r="M7" t="n">
-        <v>79000</v>
+        <v>1734000</v>
       </c>
       <c r="N7" t="n">
-        <v>23.61</v>
+        <v>50.45</v>
       </c>
       <c r="O7" t="n">
-        <v>79127864800</v>
+        <v>1430800050500</v>
       </c>
       <c r="P7" t="n">
-        <v>139200</v>
+        <v>2987000</v>
       </c>
       <c r="Q7" t="n">
-        <v>57000</v>
+        <v>274000</v>
       </c>
       <c r="R7" t="n">
-        <v>21000</v>
+        <v>281000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>146000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>두산에너빌리티, 하반기 본 수주 및 10만원 돌파 전망. 두산퓨얼셀과의 비교 및 원전 건설 관련 언급.</t>
+          <t>자사주 매입 및 외인 수급에 대한 기대감이 높으며, 200만원 돌파 가능성에 대한 긍정적인 전망이 우세합니다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['하반기 수주', '원전 건설', '10만원']</t>
+          <t>['자사주매입', '외인수급', '숏커버링']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>원익홀딩스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23400</v>
+        <v>83300</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>+4.00%</t>
+          <t>+5.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.62</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>42</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="G8" t="n">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="H8" t="n">
-        <v>5.6</v>
+        <v>23.53</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>22500</v>
+        <v>79200</v>
       </c>
       <c r="K8" t="n">
-        <v>23100</v>
+        <v>80200</v>
       </c>
       <c r="L8" t="n">
-        <v>24000</v>
+        <v>84300</v>
       </c>
       <c r="M8" t="n">
-        <v>21500</v>
+        <v>79000</v>
       </c>
       <c r="N8" t="n">
-        <v>4.98</v>
+        <v>23.61</v>
       </c>
       <c r="O8" t="n">
-        <v>87574922750</v>
+        <v>91318481500</v>
       </c>
       <c r="P8" t="n">
-        <v>50600</v>
+        <v>139200</v>
       </c>
       <c r="Q8" t="n">
-        <v>9070</v>
+        <v>57000</v>
       </c>
       <c r="R8" t="n">
-        <v>-22000</v>
+        <v>5000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>원익홀딩스, 로봇주 폭발 및 신사업 진출 재료 기반 상승 전망. 국민성장펀드 3500억 유일무이 상장사 언급.</t>
+          <t>하반기 수주 기대감 및 원전 건설 관련 모멘텀, 단기적 불안감도 상존.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['로봇주', '신사업', '국민성장펀드']</t>
+          <t>['수주', '원전', '모멘텀']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,77 +1200,77 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>030530</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>265250</v>
+        <v>13600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>+3.82%</t>
+          <t>+4.53%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>678</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>410</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>2783</v>
+        <v>177</v>
       </c>
       <c r="H9" t="n">
-        <v>46.73</v>
+        <v>1.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>255500</v>
+        <v>13010</v>
       </c>
       <c r="K9" t="n">
-        <v>267000</v>
+        <v>13420</v>
       </c>
       <c r="L9" t="n">
-        <v>268000</v>
+        <v>14100</v>
       </c>
       <c r="M9" t="n">
-        <v>264500</v>
+        <v>13410</v>
       </c>
       <c r="N9" t="n">
-        <v>46.71</v>
+        <v>1.91</v>
       </c>
       <c r="O9" t="n">
-        <v>891462676250</v>
+        <v>49637950980</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>31500</v>
       </c>
       <c r="Q9" t="n">
-        <v>69600</v>
+        <v>1252</v>
       </c>
       <c r="R9" t="n">
-        <v>710000</v>
+        <v>204000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>삼성전자, 30만원 터치 및 50~60만+a 목표주가 언급. 배당 기대와 함께 단기 매도 의견도 혼재.</t>
+          <t>미국 광통신주 상승에도 불구하고 국내 거래량 및 대금 부진으로 인한 약세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,11 +1279,11 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['목표주가', '배당', '매도']</t>
+          <t>['광통신', '거래량', '거래대금']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>100</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23850</v>
+        <v>264750</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>+1.49%</t>
+          <t>+3.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="E10" t="n">
-        <v>184</v>
+        <v>736</v>
       </c>
       <c r="F10" t="n">
-        <v>98</v>
+        <v>435</v>
       </c>
       <c r="G10" t="n">
-        <v>228</v>
+        <v>2801</v>
       </c>
       <c r="H10" t="n">
-        <v>0.16</v>
+        <v>46.73</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>23500</v>
+        <v>255500</v>
       </c>
       <c r="K10" t="n">
-        <v>23200</v>
+        <v>267000</v>
       </c>
       <c r="L10" t="n">
-        <v>25600</v>
+        <v>268000</v>
       </c>
       <c r="M10" t="n">
-        <v>22800</v>
+        <v>264500</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>46.71</v>
       </c>
       <c r="O10" t="n">
-        <v>162298431025</v>
+        <v>988809072750</v>
       </c>
       <c r="P10" t="n">
-        <v>28750</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>8200</v>
+        <v>69600</v>
       </c>
       <c r="R10" t="n">
-        <v>-13000</v>
+        <v>1074000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>809000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>스카이랩스, CART 혈압계 뉴스 언급에도 불구하고 적자 기업 고평가 및 하락 전망. 주포 변태 언급.</t>
+          <t>삼성전자, 30만원 터치 및 50~60만+a 목표주가 언급. 배당 기대와 함께 단기 매도 의견도 혼재.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['CART 혈압계', '적자 기업', '하락']</t>
+          <t>['목표주가', '배당', '매도']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>원익홀딩스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16190</v>
+        <v>23100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>+0.62%</t>
+          <t>+2.67%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F11" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16090</v>
+        <v>22500</v>
       </c>
       <c r="K11" t="n">
-        <v>16150</v>
+        <v>23100</v>
       </c>
       <c r="L11" t="n">
-        <v>16480</v>
+        <v>24000</v>
       </c>
       <c r="M11" t="n">
-        <v>15830</v>
+        <v>21500</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="O11" t="n">
-        <v>18330240905</v>
+        <v>93317591000</v>
       </c>
       <c r="P11" t="n">
-        <v>19380</v>
+        <v>50600</v>
       </c>
       <c r="Q11" t="n">
-        <v>3200</v>
+        <v>9070</v>
       </c>
       <c r="R11" t="n">
-        <v>2000</v>
+        <v>-51000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>금호건설, 9월 메가특구법 발의 및 호남 반도체 산단 인프라 언급. 일부에서는 재탕글과 하방 예상.</t>
+          <t>로봇 관련주로 인한 상승 기대감, 단기 급등 후 변동성 출현.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['메가특구법', '반도체 산단', '하방']</t>
+          <t>['로봇', '신사업', '변동성']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>030530</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>바이오니아</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10380</v>
+        <v>23650</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>205</v>
       </c>
       <c r="F12" t="n">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="G12" t="n">
-        <v>88</v>
+        <v>271</v>
       </c>
       <c r="H12" t="n">
-        <v>5.75</v>
+        <v>0.16</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10390</v>
+        <v>23500</v>
       </c>
       <c r="K12" t="n">
-        <v>10050</v>
+        <v>23200</v>
       </c>
       <c r="L12" t="n">
-        <v>11000</v>
+        <v>25600</v>
       </c>
       <c r="M12" t="n">
-        <v>9770</v>
+        <v>22800</v>
       </c>
       <c r="N12" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>14608303835</v>
+        <v>170143091300</v>
       </c>
       <c r="P12" t="n">
-        <v>15640</v>
+        <v>28750</v>
       </c>
       <c r="Q12" t="n">
-        <v>5470</v>
+        <v>8200</v>
       </c>
       <c r="R12" t="n">
-        <v>-16000</v>
+        <v>-2000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>주가 상승 및 거래량 증가에 대한 기대감 표출. 다만, 공매도 관련 부정적 언급도 존재.</t>
+          <t>CART 혈압계 관련 뉴스에도 불구하고 적자 및 고평가 논란으로 인한 하락 압력.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['주포', '공매도', '순환매']</t>
+          <t>['혈압계', '적자', '고평가']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,77 +1568,77 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>064550</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>아난티</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5410</v>
+        <v>16190</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-5.25%</t>
+          <t>+0.62%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>126</v>
+        <v>221</v>
       </c>
       <c r="H13" t="n">
-        <v>4.81</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>5710</v>
+        <v>16090</v>
       </c>
       <c r="K13" t="n">
-        <v>5640</v>
+        <v>16150</v>
       </c>
       <c r="L13" t="n">
-        <v>5650</v>
+        <v>16480</v>
       </c>
       <c r="M13" t="n">
-        <v>5270</v>
+        <v>15830</v>
       </c>
       <c r="N13" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>10064838020</v>
+        <v>20711752555</v>
       </c>
       <c r="P13" t="n">
-        <v>10480</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>3150</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-265000</v>
+        <v>-3000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>아난티, 북한 여행자 보험 및 금강산 관광 관련 언급. 외인, 연기금 매수세에도 불구하고 하락 및 주가 조작 의혹 제기.</t>
+          <t>메가특구법 발의 및 호남 반도체 산단 관련 호재 속 우상향 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['북한', '금강산', '주가 조작']</t>
+          <t>['메가특구법', '반도체 산단', '우상향']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>025980</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>본느</t>
+          <t>바이오니아</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5290</v>
+        <v>10360</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-7.84%</t>
+          <t>-0.29%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G14" t="n">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>5740</v>
+        <v>10390</v>
       </c>
       <c r="K14" t="n">
-        <v>5250</v>
+        <v>10050</v>
       </c>
       <c r="L14" t="n">
-        <v>5420</v>
+        <v>11000</v>
       </c>
       <c r="M14" t="n">
-        <v>5000</v>
+        <v>9770</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1968597240</v>
+        <v>15463626470</v>
       </c>
       <c r="P14" t="n">
-        <v>9680</v>
+        <v>15640</v>
       </c>
       <c r="Q14" t="n">
-        <v>371</v>
+        <v>5470</v>
       </c>
       <c r="R14" t="n">
-        <v>-13000</v>
+        <v>-84000</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>반기보고서 제출 지연 악재로 인한 하한가 및 급락. 조선일보 기사 인용 및 투자자들의 탈출 언급.</t>
+          <t>개인 투자자들의 긍정적인 기대감과 함께 일부 호재 가능성이 언급되고 있으나, 구체적인 근거는 부족한 상황입니다.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['반기보고서', '악재', '조선일보']</t>
+          <t>['주포', '순환매', '공매']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1751,6 +1751,190 @@
         </is>
       </c>
       <c r="Z14" t="inlineStr">
+        <is>
+          <t>064550</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>아난티</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5380</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-5.78%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E15" t="n">
+        <v>45</v>
+      </c>
+      <c r="F15" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" t="n">
+        <v>149</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>5710</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5640</v>
+      </c>
+      <c r="L15" t="n">
+        <v>5650</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5270</v>
+      </c>
+      <c r="N15" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="O15" t="n">
+        <v>10480719635</v>
+      </c>
+      <c r="P15" t="n">
+        <v>10480</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3150</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-307000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>북한 관련 기대감 약화 및 연이은 하락세, 외인 매수세 유입에도 반등 모색.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['북한', '금강산', '외인 매수']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>025980</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>본느</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5310</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-7.49%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>70</v>
+      </c>
+      <c r="F16" t="n">
+        <v>37</v>
+      </c>
+      <c r="G16" t="n">
+        <v>148</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>5740</v>
+      </c>
+      <c r="K16" t="n">
+        <v>5250</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5420</v>
+      </c>
+      <c r="M16" t="n">
+        <v>5000</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2073256090</v>
+      </c>
+      <c r="P16" t="n">
+        <v>9680</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>371</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>반기보고서 제출 지연 및 악재 뉴스 발생으로 주가 하락에 대한 우려가 크며, 상폐 가능성까지 제기되고 있습니다.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['반기보고서', '악재뉴스', '상폐']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
         <is>
           <t>226340</t>
         </is>
